--- a/employee_surveys/035_employee_reward_preference_poll--employee_surveys.xlsx
+++ b/employee_surveys/035_employee_reward_preference_poll--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gift_card'}</t>
+          <t>gift_card</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Gift Card'}</t>
+          <t>Gift Card</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'extra_vacation_time'}</t>
+          <t>extra_vacation_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Extra Vacation Time'}</t>
+          <t>Extra Vacation Time</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monetary_bonus'}</t>
+          <t>monetary_bonus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monetary Bonus'}</t>
+          <t>Monetary Bonus</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Text Message'}</t>
+          <t>Text Message</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in-app'}</t>
+          <t>in-app</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In-app'}</t>
+          <t>In-app</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'push_notification'}</t>
+          <t>push_notification</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Push Notification'}</t>
+          <t>Push Notification</t>
         </is>
       </c>
     </row>
